--- a/examples/demos/02_fit_distributions.xlsx
+++ b/examples/demos/02_fit_distributions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834FF156-7F88-4960-A2BA-7DC16B0DDBBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656C8A74-DF27-4A3F-AD24-BDB0203CA5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,7 +106,7 @@
     <t>Write the winner into the model.</t>
   </si>
   <si>
-    <t>PROMPT →  Write the best-fitting distribution, fitted to that data with parameter uncertainty, into Model!B6 — for real, not a preview.</t>
+    <t>PROMPT →  Write the best-fitting distribution, fitted to that data with parameter uncertainty, into Model!B6 as a distribution OBJECT (the object form is what analytic questions need) — for real, not a preview.</t>
   </si>
   <si>
     <t>Expected: Model!B6 now holds a Vose&lt;Family&gt;Fit(...) formula linked to the data (fit_distribution_to_data).</t>
@@ -361,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -388,13 +388,11 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -713,16 +711,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="16"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="15" t="s">
@@ -927,7 +925,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A49" s="14"/>
       <c r="B49" s="8" t="s">
         <v>38</v>
@@ -968,20 +966,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
@@ -3937,40 +3935,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="4" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">

--- a/examples/demos/02_fit_distributions.xlsx
+++ b/examples/demos/02_fit_distributions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656C8A74-DF27-4A3F-AD24-BDB0203CA5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8E879D-378A-40D9-B56D-EF01F5E1D8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -389,10 +389,10 @@
     <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -711,13 +711,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="16"/>
